--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -12062,12 +12062,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Final Boss</t>
+          <t>The Pale Choirbeast</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>최종보스</t>
+          <t>The Pale Choirbeast</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Mini Boss</t>
+          <t>Palehorn</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>미니보스</t>
+          <t>Palehorn</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">

--- a/datafiles/localization/game_text.xlsx
+++ b/datafiles/localization/game_text.xlsx
@@ -28465,12 +28465,12 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>menu.main.option.0</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>menu.main.option.0</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="J575" t="inlineStr">
@@ -28518,12 +28518,12 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>New Game</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>새로운 게임</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="J576" t="inlineStr">
@@ -28576,7 +28576,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>딱딱한</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="J577" t="inlineStr">
